--- a/reports/gms_17_20260319.xlsx
+++ b/reports/gms_17_20260319.xlsx
@@ -508,377 +508,385 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⁠000533</t>
+          <t>⁠300139</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>顺钠股份</t>
+          <t>晓程科技</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>左侧</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>58.66</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8.2100</t>
+          <t>-0.8100</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>13</v>
+      </c>
+      <c r="H2" t="n">
         <v>7</v>
       </c>
-      <c r="H2" t="n">
-        <v>13</v>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>67.47</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>58.24%</t>
+          <t>-1.20%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>41.57%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>71.14%</t>
+          <t>-1.36%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>-3.80%</t>
+          <t>-5.22%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分70.0 蓄势70.0(引力20.0+平衡20.0+量缩30.0)A 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>⁠000558</t>
+          <t>⁠600307</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>天府文旅</t>
+          <t>酒钢宏兴</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>右侧</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.8700</t>
+          <t>0.4400</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-17.64%</t>
+          <t>22.49%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-18.51%</t>
+          <t>19.30%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-15.62%</t>
+          <t>23.91%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>-5.79%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分60.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量60.0(推力0.0+支撑30.0+攻击30.0)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>⁠000651</t>
+          <t>⁠000533</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>格力电器</t>
+          <t>顺钠股份</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>左侧</t>
+          <t>右侧</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>18.58</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.2200</t>
+          <t>7.6600</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>14.45</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>53.02%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>41.23%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>70.15%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>-5.92%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>总分70.0 蓄势70.0(引力0.0+平衡40.0+量缩30.0)A 动量70.0(推力40.0+支撑30.0+攻击0.0)</t>
+          <t>总分50.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量50.0(推力0.0+支撑30.0+攻击20.0)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>⁠000709</t>
+          <t>⁠002155</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>河钢股份</t>
+          <t>湖南黄金</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>29.60</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0400</t>
+          <t>-4.3000</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>-12.23%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>-14.53%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>-12.68%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-1.96%</t>
+          <t>-6.00%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量30.0(推力40.0+支撑-10.0+攻击0.0)</t>
+          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>⁠000721</t>
+          <t>⁠300058</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>西安饮食</t>
+          <t>蓝色光标</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.8700</t>
+          <t>-3.9500</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>17.04</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-10.18%</t>
+          <t>-23.19%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-10.55%</t>
+          <t>-26.39%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-9.54%</t>
+          <t>-20.88%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>-1.08%</t>
+          <t>-3.29%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>⁠000905</t>
+          <t>⁠300223</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>厦门港务</t>
+          <t>北京君正</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>121.92</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.9300</t>
+          <t>1.2200</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -889,22 +897,22 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>125.79</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-7.48%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-8.14%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-7.53%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -914,97 +922,93 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-6.67%</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分50.0 蓄势40.0(引力0.0+平衡40.0+量缩0.0) 动量50.0(推力40.0+支撑-10.0+攻击20.0)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>⁠000983</t>
+          <t>⁠603667</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>山西焦煤</t>
+          <t>五洲新春</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>70.0%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>左侧</t>
-        </is>
-      </c>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>66.92</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.0400</t>
+          <t>-20.5300</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>76.81</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-26.73%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>-30.68%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>-23.48%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-2.67%</t>
+          <t>-4.33%</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>总分70.0 蓄势70.0(引力0.0+平衡40.0+量缩30.0)A 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>⁠002050</t>
+          <t>⁠688291</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>三花智控</t>
+          <t>金橙子</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1015,48 +1019,48 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>46.41</t>
+          <t>39.65</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-6.8900</t>
+          <t>-5.1300</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>49.56</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-13.90%</t>
+          <t>-11.07%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-14.85%</t>
+          <t>-12.94%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-12.93%</t>
+          <t>-11.46%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>-3.01%</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1068,235 +1072,235 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>⁠002155</t>
+          <t>⁠000651</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>湖南黄金</t>
+          <t>格力电器</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>38.56</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.4700</t>
+          <t>-0.1600</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>37.94</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-6.98%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-7.84%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-7.27%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分40.0 蓄势40.0(引力0.0+平衡40.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>⁠002171</t>
+          <t>⁠002709</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>楚江新材</t>
+          <t>天赐材料</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>41.36</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.9400</t>
+          <t>-0.1500</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
         <v>10</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>43.68</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-7.31%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-7.91%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-7.33%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-6.70%</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分40.0 蓄势40.0(引力0.0+平衡40.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>⁠002230</t>
+          <t>⁠000558</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>科大讯飞</t>
+          <t>天府文旅</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>51.58</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-5.2800</t>
+          <t>-0.8100</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>54.22</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-9.74%</t>
+          <t>-16.59%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-10.24%</t>
+          <t>-17.72%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-9.29%</t>
+          <t>-15.06%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>⁠002271</t>
+          <t>⁠002050</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>东方雨虹</t>
+          <t>三花智控</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15.72</t>
+          <t>44.98</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1.9800</t>
+          <t>-7.1800</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1307,22 +1311,22 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-11.48%</t>
+          <t>-14.61%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-12.60%</t>
+          <t>-15.96%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-11.19%</t>
+          <t>-13.77%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1332,247 +1336,247 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-3.08%</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>⁠002364</t>
+          <t>⁠002230</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>中恒电气</t>
+          <t>科大讯飞</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.23</t>
+          <t>50.36</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.7200</t>
+          <t>-6.1100</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>53.90</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-2.12%</t>
+          <t>-11.34%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-12.13%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-2.25%</t>
+          <t>-10.82%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>-2.37%</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>⁠002557</t>
+          <t>⁠300919</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>洽洽食品</t>
+          <t>中伟新材</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>47.85</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-1.1200</t>
+          <t>-7.2100</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>22.89</t>
+          <t>53.62</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-4.89%</t>
+          <t>-13.45%</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-4.97%</t>
+          <t>-15.07%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-4.74%</t>
+          <t>-13.09%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>-3.92%</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>⁠002709</t>
+          <t>⁠600570</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>天赐材料</t>
+          <t>恒生电子</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>44.33</t>
+          <t>27.16</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3.4200</t>
+          <t>-3.6000</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>43.66</t>
+          <t>28.58</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>7.83%</t>
+          <t>-12.60%</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>7.71%</t>
+          <t>-13.25%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8.36%</t>
+          <t>-11.70%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-2.74%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>⁠00700</t>
+          <t>⁠601231</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>腾讯控股</t>
+          <t>环旭电子</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>550.50</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>15.0000</t>
+          <t>-2.3700</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1583,22 +1587,22 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>529.67</t>
+          <t>41.30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>-5.74%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>-6.61%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>-6.20%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1608,162 +1612,162 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>-2.90%</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>总分70.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量70.0(推力40.0+支撑30.0+攻击0.0)</t>
+          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>⁠00981</t>
+          <t>⁠603583</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>中芯国际</t>
+          <t>捷昌驱动</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>61.70</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-8.3000</t>
+          <t>-4.1100</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>65.30</t>
+          <t>35.36</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-12.71%</t>
+          <t>-11.62%</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-13.45%</t>
+          <t>-12.47%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-11.86%</t>
+          <t>-11.09%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-2.23%</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>总分60.0 蓄势60.0(引力30.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>⁠01810</t>
+          <t>⁠603933</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>小米集团－Ｗ</t>
+          <t>睿能科技</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>35.14</t>
+          <t>21.20</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.9600</t>
+          <t>-2.0000</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>34.59</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-5.67%</t>
+          <t>-8.92%</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-5.58%</t>
+          <t>-9.43%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-5.28%</t>
+          <t>-8.62%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分35.0 蓄势35.0(引力20.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>⁠02269</t>
+          <t>⁠002364</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>药明生物</t>
+          <t>中恒电气</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1774,48 +1778,48 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-5.8800</t>
+          <t>-1.4700</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>11</v>
       </c>
       <c r="H20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>33.94</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-15.55%</t>
+          <t>-4.33%</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-16.55%</t>
+          <t>-4.85%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-14.20%</t>
+          <t>-4.62%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>-2.91%</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1827,12 +1831,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>⁠02565</t>
+          <t>⁠300750</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>派格生物医药－Ｂ</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1843,203 +1847,203 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>56.25</t>
+          <t>400.50</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-11.2500</t>
+          <t>32.5000</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>60.20</t>
+          <t>369.18</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-18.69%</t>
+          <t>8.80%</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-20.00%</t>
+          <t>8.11%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-16.67%</t>
+          <t>8.83%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>⁠02899</t>
+          <t>⁠301275</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>汉朔科技</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>41.94</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-6.1800</t>
+          <t>-16.8500</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>41.62</t>
+          <t>51.63</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-14.85%</t>
+          <t>-32.63%</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-16.55%</t>
+          <t>-40.18%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-14.20%</t>
+          <t>-28.66%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>-5.54%</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势30.0(引力30.0+平衡0.0+量缩0.0) 动量20.0(推力0.0+支撑-10.0+攻击30.0)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>⁠03690</t>
+          <t>⁠600105</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>美团－Ｗ</t>
+          <t>永鼎股份</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.30</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-8.5500</t>
+          <t>-0.7400</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>79.86</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-10.71%</t>
+          <t>-2.65%</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-10.65%</t>
+          <t>-2.74%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-9.62%</t>
+          <t>-2.67%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量15.0(推力0.0+支撑15.0+攻击0.0)</t>
+          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>⁠03750</t>
+          <t>⁠600525</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>ST长园</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2050,12 +2054,12 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>650.50</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>143.5000</t>
+          <t>0.9400</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -2066,22 +2070,22 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>543.91</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>26.38%</t>
+          <t>17.69%</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>22.06%</t>
+          <t>17.18%</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>28.30%</t>
+          <t>20.75%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2091,178 +2095,178 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>-1.79%</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分30.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>⁠09988</t>
+          <t>⁠688498</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>阿里巴巴－Ｗ</t>
+          <t>源杰科技</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>137.70</t>
+          <t>950.00</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-22.4000</t>
+          <t>212.4000</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>140.54</t>
+          <t>842.97</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-15.94%</t>
+          <t>25.20%</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>-16.27%</t>
+          <t>22.36%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-13.99%</t>
+          <t>28.80%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>6.86%</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>⁠300058</t>
+          <t>⁠000721</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>蓝色光标</t>
+          <t>西安饮食</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-4.1400</t>
+          <t>-0.8800</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>17.27</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-23.97%</t>
+          <t>-10.36%</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-26.74%</t>
+          <t>-10.88%</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-21.10%</t>
+          <t>-9.81%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>⁠300139</t>
+          <t>⁠002271</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>晓程科技</t>
+          <t>东方雨虹</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>61.89</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>3.8100</t>
+          <t>-3.0200</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -2273,22 +2277,22 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>67.44</t>
+          <t>17.11</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>5.65%</t>
+          <t>-17.65%</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>-20.34%</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>6.56%</t>
+          <t>-16.90%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2298,316 +2302,316 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-2.50%</t>
+          <t>-5.53%</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>⁠300223</t>
+          <t>⁠002557</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>北京君正</t>
+          <t>洽洽食品</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>130.63</t>
+          <t>21.75</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>8.4400</t>
+          <t>-1.8600</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>125.80</t>
+          <t>22.79</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>6.71%</t>
+          <t>-8.16%</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>6.46%</t>
+          <t>-8.55%</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>6.91%</t>
+          <t>-7.88%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>5.04%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量15.0(推力0.0+支撑15.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>⁠300699</t>
+          <t>⁠601138</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>光威复材</t>
+          <t>工业富联</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>37.00</t>
+          <t>50.46</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.0000</t>
+          <t>-4.7400</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H29" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>38.78</t>
+          <t>54.33</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-5.16%</t>
+          <t>-8.72%</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-5.41%</t>
+          <t>-9.39%</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-5.13%</t>
+          <t>-8.59%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>-4.17%</t>
+          <t>-3.07%</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>⁠300705</t>
+          <t>⁠688114</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>九典制药</t>
+          <t>华大智造</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>52.55</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.6700</t>
+          <t>-14.5200</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H30" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15.10</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-4.44%</t>
+          <t>-24.57%</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-4.52%</t>
+          <t>-27.63%</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-4.32%</t>
+          <t>-21.65%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>-1.78%</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>⁠300750</t>
+          <t>⁠688981</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>中芯国际</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>402.02</t>
+          <t>105.96</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>37.0500</t>
+          <t>-9.0500</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>367.40</t>
+          <t>110.34</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>10.08%</t>
+          <t>-8.20%</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>9.22%</t>
+          <t>-8.54%</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>10.15%</t>
+          <t>-7.87%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>-0.74%</t>
+          <t>-0.60%</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>⁠300919</t>
+          <t>⁠920263</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>中伟新材</t>
+          <t>中航泰达</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>49.80</t>
+          <t>10.81</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.8600</t>
+          <t>-2.0900</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2618,22 +2622,22 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>53.76</t>
+          <t>12.59</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-1.60%</t>
+          <t>-16.60%</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-19.33%</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-16.20%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2643,990 +2647,994 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>-3.14%</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分20.0 蓄势20.0(引力20.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>⁠301275</t>
+          <t>⁠000905</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>汉朔科技</t>
+          <t>厦门港务</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>44.40</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-15.2500</t>
+          <t>-1.2400</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>52.52</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-29.04%</t>
+          <t>-10.03%</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>-34.35%</t>
+          <t>-11.22%</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-25.57%</t>
+          <t>-10.09%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-3.24%</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>总分60.0 蓄势60.0(引力30.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>⁠600105</t>
+          <t>⁠000983</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>永鼎股份</t>
+          <t>山西焦煤</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>27.49</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.0900</t>
+          <t>-0.1300</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H34" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>27.99</t>
+          <t>7.22</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-3.89%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>-3.97%</t>
+          <t>-1.88%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-3.81%</t>
+          <t>-1.84%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>⁠600307</t>
+          <t>⁠688256</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>酒钢宏兴</t>
+          <t>寒武纪</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1037.02</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.5800</t>
+          <t>-41.8800</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1116.91</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>29.98%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>23.97%</t>
+          <t>-4.04%</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>31.52%</t>
+          <t>-3.88%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>10.00%</t>
+          <t>-2.72%</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>⁠600525</t>
+          <t>⁠688795</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ST长园</t>
+          <t>摩尔线程</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>548.70</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.9400</t>
+          <t>-15.3000</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>573.17</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>17.84%</t>
+          <t>-2.67%</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>16.88%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>20.30%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>-2.45%</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分15.0 蓄势15.0(引力0.0+平衡0.0+量缩15.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>⁠600570</t>
+          <t>⁠000709</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>恒生电子</t>
+          <t>河钢股份</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27.52</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-3.3300</t>
+          <t>-0.0900</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-11.58%</t>
+          <t>-3.52%</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>-12.10%</t>
+          <t>-3.72%</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-10.79%</t>
+          <t>-3.59%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-3.20%</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>⁠600838</t>
+          <t>⁠002171</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>上海九百</t>
+          <t>楚江新材</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-0.3800</t>
+          <t>-1.6100</t>
         </is>
       </c>
       <c r="G38" t="n">
+        <v>9</v>
+      </c>
+      <c r="H38" t="n">
         <v>10</v>
       </c>
-      <c r="H38" t="n">
-        <v>9</v>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>12.78</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-12.60%</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>-3.42%</t>
+          <t>-14.25%</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-3.31%</t>
+          <t>-12.47%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>-4.88%</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量15.0(推力0.0+支撑15.0+攻击0.0)</t>
+          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>⁠600966</t>
+          <t>⁠300699</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>博汇纸业</t>
+          <t>光威复材</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>8.16</t>
+          <t>34.79</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.5400</t>
+          <t>-4.5100</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>6.58%</t>
+          <t>-11.69%</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>6.62%</t>
+          <t>-12.96%</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>-11.48%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>-5.97%</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>⁠601138</t>
+          <t>⁠300705</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>工业富联</t>
+          <t>九典制药</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>52.06</t>
+          <t>14.51</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-4.0100</t>
+          <t>-1.0200</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H40" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>54.61</t>
+          <t>15.05</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>-7.34%</t>
+          <t>-6.78%</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>-7.70%</t>
+          <t>-7.03%</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-7.15%</t>
+          <t>-6.57%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>-2.16%</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>⁠601231</t>
+          <t>⁠600838</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>环旭电子</t>
+          <t>上海九百</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>10.90</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.8500</t>
+          <t>-0.7400</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>41.40</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-2.05%</t>
+          <t>-6.76%</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>-2.30%</t>
+          <t>-6.79%</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-2.25%</t>
+          <t>-6.36%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>-1.89%</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>⁠601636</t>
+          <t>⁠600966</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>旗滨集团</t>
+          <t>博汇纸业</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.7400</t>
+          <t>-0.6600</t>
         </is>
       </c>
       <c r="G42" t="n">
         <v>11</v>
       </c>
       <c r="H42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-10.44%</t>
+          <t>-8.05%</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>-11.46%</t>
+          <t>-8.99%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-10.28%</t>
+          <t>-8.25%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>-1.67%</t>
+          <t>-10.05%</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>⁠603583</t>
+          <t>⁠601636</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>捷昌驱动</t>
+          <t>旗滨集团</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>33.70</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-3.7200</t>
+          <t>-1.2700</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H43" t="n">
         <v>8</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>35.58</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-10.46%</t>
+          <t>-18.05%</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-11.04%</t>
+          <t>-20.42%</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-9.94%</t>
+          <t>-16.96%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>-3.71%</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>⁠603667</t>
+          <t>⁠688066</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>五洲新春</t>
+          <t>航天宏图</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>69.95</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-21.2300</t>
+          <t>-1.3700</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H44" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>78.02</t>
+          <t>24.06</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-27.21%</t>
+          <t>-5.69%</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>-30.35%</t>
+          <t>-5.97%</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-23.28%</t>
+          <t>-5.63%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分0.0 蓄势0.0(引力0.0+平衡0.0+量缩0.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>⁠603933</t>
+          <t>⁠01810</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>睿能科技</t>
+          <t>小米集团－Ｗ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>左侧</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>21.88</t>
+          <t>36.32</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.7100</t>
+          <t>-0.2000</t>
         </is>
       </c>
       <c r="G45" t="n">
         <v>11</v>
       </c>
       <c r="H45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>34.55</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-7.59%</t>
+          <t>-0.58%</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>-7.82%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-7.25%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>3.36%</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分70.0 蓄势70.0(引力0.0+平衡40.0+量缩30.0)A 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>⁠688066</t>
+          <t>⁠00981</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>航天宏图</t>
+          <t>中芯国际</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>59.75</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.8500</t>
+          <t>-10.0500</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>64.78</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-7.66%</t>
+          <t>-15.51%</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>-8.09%</t>
+          <t>-16.82%</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-7.48%</t>
+          <t>-14.40%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>-3.16%</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分60.0 蓄势60.0(引力30.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>⁠688114</t>
+          <t>⁠00700</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>华大智造</t>
+          <t>腾讯控股</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3637,48 +3645,48 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>53.50</t>
+          <t>513.00</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-14.1500</t>
+          <t>-19.0000</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H47" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>59.85</t>
+          <t>528.55</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-23.64%</t>
+          <t>-3.59%</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>-26.45%</t>
+          <t>-3.70%</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-20.92%</t>
+          <t>-3.57%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>-0.76%</t>
+          <t>-6.81%</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3690,81 +3698,81 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>⁠688256</t>
+          <t>⁠02269</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>寒武纪</t>
+          <t>药明生物</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1066.00</t>
+          <t>34.12</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-34.9000</t>
+          <t>-7.2200</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1120.10</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-3.12%</t>
+          <t>-19.28%</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>-3.27%</t>
+          <t>-21.16%</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-3.17%</t>
+          <t>-17.46%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-3.94%</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>⁠688291</t>
+          <t>⁠02899</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>金橙子</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3775,12 +3783,12 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>40.88</t>
+          <t>34.70</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-4.2800</t>
+          <t>-10.3200</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3791,22 +3799,22 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>46.62</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-9.18%</t>
+          <t>-25.06%</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>-10.47%</t>
+          <t>-29.74%</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-9.48%</t>
+          <t>-22.92%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3816,7 +3824,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>-7.07%</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -3828,150 +3836,150 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>⁠688498</t>
+          <t>⁠03690</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>源杰科技</t>
+          <t>美团－Ｗ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>889.00</t>
+          <t>80.70</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>119.0100</t>
+          <t>-4.1500</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>833.97</t>
+          <t>79.45</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>14.27%</t>
+          <t>-5.22%</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>13.39%</t>
+          <t>-5.14%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>15.46%</t>
+          <t>-4.89%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>7.08%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
+          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量15.0(推力0.0+支撑15.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>⁠688795</t>
+          <t>⁠09988</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>摩尔线程</t>
+          <t>阿里巴巴－Ｗ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>562.50</t>
+          <t>132.00</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-10.5000</t>
+          <t>-26.6000</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H51" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>574.38</t>
+          <t>139.13</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>-1.83%</t>
+          <t>-19.12%</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>-20.15%</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-1.83%</t>
+          <t>-16.77%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>-4.14%</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>⁠688981</t>
+          <t>⁠02565</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>中芯国际</t>
+          <t>派格生物医药－Ｂ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3982,12 +3990,12 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>106.60</t>
+          <t>55.85</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-9.6000</t>
+          <t>-10.9000</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3998,22 +4006,22 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>110.85</t>
+          <t>59.61</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>-8.66%</t>
+          <t>-18.28%</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>-9.01%</t>
+          <t>-19.52%</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-8.26%</t>
+          <t>-16.33%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4023,7 +4031,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4035,69 +4043,69 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>⁠920263</t>
+          <t>⁠03750</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>中航泰达</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>11.16</t>
+          <t>644.00</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-1.6500</t>
+          <t>116.0000</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H53" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>550.76</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>-13.01%</t>
+          <t>21.06%</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>-14.78%</t>
+          <t>18.01%</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-12.88%</t>
+          <t>21.97%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>-1.00%</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>总分50.0 蓄势50.0(引力20.0+平衡0.0+量缩30.0) 动量-10.0(推力0.0+支撑-10.0+攻击0.0)</t>
+          <t>总分30.0 蓄势30.0(引力0.0+平衡0.0+量缩30.0) 动量30.0(推力0.0+支撑30.0+攻击0.0)</t>
         </is>
       </c>
     </row>
